--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119835339</v>
+        <v>119834478</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>90582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563072</v>
+        <v>562990</v>
       </c>
       <c r="R2" t="n">
-        <v>6509961</v>
+        <v>6509965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834500</v>
+        <v>119835339</v>
       </c>
       <c r="B3" t="n">
-        <v>90582</v>
+        <v>91185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562990</v>
+        <v>563072</v>
       </c>
       <c r="R3" t="n">
-        <v>6509965</v>
+        <v>6509961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834478</v>
+        <v>119834500</v>
       </c>
       <c r="B2" t="n">
         <v>90582</v>

--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119834500</v>
       </c>
       <c r="B2" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>119835339</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91203</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834500</v>
+        <v>119835339</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>91203</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562990</v>
+        <v>563072</v>
       </c>
       <c r="R2" t="n">
-        <v>6509965</v>
+        <v>6509961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119835339</v>
+        <v>119834478</v>
       </c>
       <c r="B3" t="n">
-        <v>91203</v>
+        <v>90600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563072</v>
+        <v>562990</v>
       </c>
       <c r="R3" t="n">
-        <v>6509961</v>
+        <v>6509965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119835339</v>
+        <v>131734496</v>
       </c>
       <c r="B2" t="n">
-        <v>91203</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnkärret, Kvarnkärret, Ög</t>
+          <t>Kvarnkärret Nordväst, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563072</v>
+        <v>563098</v>
       </c>
       <c r="R2" t="n">
-        <v>6509961</v>
+        <v>6509881</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kransmossa i botten av bäckravin.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +765,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Blixt</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>119834478</v>
       </c>
       <c r="B3" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,6 +875,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119835339</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnkärret, Kvarnkärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563072</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6509961</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Frida Blixt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60171-2023 artfynd.xlsx
+++ b/artfynd/A 60171-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734496</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119834478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,8 +987,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119835339</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>